--- a/data/random_collections/Primeseq_Nextgen_deML_and_sample_origin.xlsx
+++ b/data/random_collections/Primeseq_Nextgen_deML_and_sample_origin.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$98</definedName>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="267">
   <si>
     <t>deML</t>
   </si>
@@ -807,6 +808,27 @@
   </si>
   <si>
     <t>Human, Macaque</t>
+  </si>
+  <si>
+    <t>Bioanalyzer</t>
+  </si>
+  <si>
+    <t>ave size</t>
+  </si>
+  <si>
+    <t>213-706</t>
+  </si>
+  <si>
+    <t>size distribution CV</t>
+  </si>
+  <si>
+    <t>old ave</t>
+  </si>
+  <si>
+    <t>new ave</t>
+  </si>
+  <si>
+    <t>ave size dis</t>
   </si>
 </sst>
 </file>
@@ -5451,4 +5473,4397 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>196</v>
+      </c>
+      <c r="O2" t="s">
+        <v>250</v>
+      </c>
+      <c r="P2" t="s">
+        <v>249</v>
+      </c>
+      <c r="T2" t="s">
+        <v>260</v>
+      </c>
+      <c r="U2" t="s">
+        <v>261</v>
+      </c>
+      <c r="V2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>32136451</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="D3">
+        <v>30773218</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>539111714</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>400000000</v>
+      </c>
+      <c r="M3">
+        <v>1.35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>197</v>
+      </c>
+      <c r="O3" t="s">
+        <v>198</v>
+      </c>
+      <c r="P3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>271941043</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="D4">
+        <v>265905791</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>317409356</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>400000000</v>
+      </c>
+      <c r="M4">
+        <v>0.79</v>
+      </c>
+      <c r="N4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>305569190</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D5">
+        <v>298416896</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>470365688</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>400000000</v>
+      </c>
+      <c r="M5">
+        <v>1.18</v>
+      </c>
+      <c r="N5" t="s">
+        <v>197</v>
+      </c>
+      <c r="O5" t="s">
+        <v>199</v>
+      </c>
+      <c r="P5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>144327591</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.307</v>
+      </c>
+      <c r="D6">
+        <v>138264729</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>470365688</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>400000000</v>
+      </c>
+      <c r="M6">
+        <v>1.18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>197</v>
+      </c>
+      <c r="O6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>177341863</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="D7">
+        <v>172364539</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7">
+        <v>347977561</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>400000000</v>
+      </c>
+      <c r="M7">
+        <v>0.87</v>
+      </c>
+      <c r="N7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>161454459</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="D8">
+        <v>155283744</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>347977561</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>400000000</v>
+      </c>
+      <c r="M8">
+        <v>0.87</v>
+      </c>
+      <c r="N8" t="s">
+        <v>197</v>
+      </c>
+      <c r="T8" t="s">
+        <v>262</v>
+      </c>
+      <c r="U8">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>271370358</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="D9">
+        <v>265008925</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9">
+        <v>368920108</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>400000000</v>
+      </c>
+      <c r="M9">
+        <v>0.92</v>
+      </c>
+      <c r="N9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>92773658</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.251</v>
+      </c>
+      <c r="D10">
+        <v>90236302</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10">
+        <v>368920108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10">
+        <v>400000000</v>
+      </c>
+      <c r="M10">
+        <v>0.92</v>
+      </c>
+      <c r="N10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>236697944</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="D11">
+        <v>231184434</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11">
+        <v>368920108</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11">
+        <v>400000000</v>
+      </c>
+      <c r="M11">
+        <v>0.92</v>
+      </c>
+      <c r="N11" t="s">
+        <v>204</v>
+      </c>
+      <c r="O11" t="s">
+        <v>200</v>
+      </c>
+      <c r="P11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12">
+        <v>152781953</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="D12">
+        <v>148704508</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12">
+        <v>368920108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12">
+        <v>400000000</v>
+      </c>
+      <c r="M12">
+        <v>0.92</v>
+      </c>
+      <c r="N12" t="s">
+        <v>197</v>
+      </c>
+      <c r="O12" t="s">
+        <v>198</v>
+      </c>
+      <c r="P12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>343010943</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="D13">
+        <v>330987390</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13">
+        <v>1166367326</v>
+      </c>
+      <c r="K13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13">
+        <v>1200000000</v>
+      </c>
+      <c r="M13">
+        <v>0.97</v>
+      </c>
+      <c r="N13" t="s">
+        <v>204</v>
+      </c>
+      <c r="O13" t="s">
+        <v>199</v>
+      </c>
+      <c r="P13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14">
+        <v>34758061</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="D14">
+        <v>32858555</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14">
+        <v>1166367326</v>
+      </c>
+      <c r="K14" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14">
+        <v>1200000000</v>
+      </c>
+      <c r="M14">
+        <v>0.97</v>
+      </c>
+      <c r="N14" t="s">
+        <v>230</v>
+      </c>
+      <c r="O14" t="s">
+        <v>207</v>
+      </c>
+      <c r="P14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15">
+        <v>390438162</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="D15">
+        <v>370310835</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15">
+        <v>1105359231</v>
+      </c>
+      <c r="K15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15">
+        <v>1200000000</v>
+      </c>
+      <c r="M15">
+        <v>0.92</v>
+      </c>
+      <c r="N15" t="s">
+        <v>231</v>
+      </c>
+      <c r="O15" t="s">
+        <v>231</v>
+      </c>
+      <c r="P15" t="s">
+        <v>208</v>
+      </c>
+      <c r="U15">
+        <v>419</v>
+      </c>
+      <c r="V15">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16">
+        <v>334515519</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="D16">
+        <v>315478109</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16">
+        <v>1105359231</v>
+      </c>
+      <c r="K16" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16">
+        <v>1200000000</v>
+      </c>
+      <c r="M16">
+        <v>0.92</v>
+      </c>
+      <c r="N16" t="s">
+        <v>232</v>
+      </c>
+      <c r="O16" t="s">
+        <v>232</v>
+      </c>
+      <c r="P16" t="s">
+        <v>208</v>
+      </c>
+      <c r="U16">
+        <v>408</v>
+      </c>
+      <c r="V16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>287276297</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="D17">
+        <v>273606978</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17">
+        <v>1105359231</v>
+      </c>
+      <c r="K17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17">
+        <v>1200000000</v>
+      </c>
+      <c r="M17">
+        <v>0.92</v>
+      </c>
+      <c r="N17" t="s">
+        <v>233</v>
+      </c>
+      <c r="O17" t="s">
+        <v>233</v>
+      </c>
+      <c r="P17" t="s">
+        <v>208</v>
+      </c>
+      <c r="U17">
+        <v>440</v>
+      </c>
+      <c r="V17">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <v>36904796</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="D18">
+        <v>34605424</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18">
+        <v>1105359231</v>
+      </c>
+      <c r="K18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18">
+        <v>1200000000</v>
+      </c>
+      <c r="M18">
+        <v>0.92</v>
+      </c>
+      <c r="N18" t="s">
+        <v>204</v>
+      </c>
+      <c r="O18" t="s">
+        <v>209</v>
+      </c>
+      <c r="P18" t="s">
+        <v>210</v>
+      </c>
+      <c r="U18">
+        <v>460</v>
+      </c>
+      <c r="V18">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>358896712</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="D19">
+        <v>350899341</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F19">
+        <v>6799587</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19">
+        <v>449351062</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19">
+        <v>400000000</v>
+      </c>
+      <c r="M19">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="N19" t="s">
+        <v>204</v>
+      </c>
+      <c r="O19" t="s">
+        <v>211</v>
+      </c>
+      <c r="P19" t="s">
+        <v>212</v>
+      </c>
+      <c r="U19">
+        <v>424</v>
+      </c>
+      <c r="V19">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20">
+        <v>77027107</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="D20">
+        <v>74323045</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="F20">
+        <v>2010175</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20">
+        <v>449351062</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20">
+        <v>400000000</v>
+      </c>
+      <c r="M20">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="N20" t="s">
+        <v>197</v>
+      </c>
+      <c r="O20" t="s">
+        <v>236</v>
+      </c>
+      <c r="P20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>10788820</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D21">
+        <v>8231356</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="F21">
+        <v>2419787</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="H21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21">
+        <v>410323761</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21">
+        <v>400000000</v>
+      </c>
+      <c r="M21">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22">
+        <v>164107379</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D22">
+        <v>106486019</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F22">
+        <v>56190660</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22">
+        <v>410323761</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22">
+        <v>400000000</v>
+      </c>
+      <c r="M22">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="s">
+        <v>235</v>
+      </c>
+      <c r="O22" t="s">
+        <v>235</v>
+      </c>
+      <c r="P22" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23">
+        <v>29350979</v>
+      </c>
+      <c r="C23" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D23">
+        <v>27855277</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F23">
+        <v>1006525</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23">
+        <v>410323761</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <v>400000000</v>
+      </c>
+      <c r="M23">
+        <v>1.03</v>
+      </c>
+      <c r="Z23" s="3">
+        <f>AVERAGE(U14:U38)</f>
+        <v>429.16666666666669</v>
+      </c>
+      <c r="AA23" s="3">
+        <f>_xlfn.STDEV.P(U14:U38)</f>
+        <v>16.697471531808507</v>
+      </c>
+      <c r="AB23" s="3">
+        <f>AVERAGE(V15:V39)</f>
+        <v>21.616666666666664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24">
+        <v>24247330</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="D24">
+        <v>14972462</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="F24">
+        <v>8951796</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24">
+        <v>410323761</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24">
+        <v>400000000</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25">
+        <v>20760210</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D25">
+        <v>19584258</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F25">
+        <v>913824</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25">
+        <v>410323761</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25">
+        <v>400000000</v>
+      </c>
+      <c r="M25">
+        <v>1.03</v>
+      </c>
+      <c r="Z25" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>20623773</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D26">
+        <v>19472884</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F26">
+        <v>929492</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26">
+        <v>410323761</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26">
+        <v>400000000</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="Z26" s="3">
+        <f>AVERAGE(U44:U55)</f>
+        <v>422.8</v>
+      </c>
+      <c r="AA26" s="3">
+        <f>_xlfn.STDEV.P(U44:U55)</f>
+        <v>13.934130758680283</v>
+      </c>
+      <c r="AB26" s="3">
+        <f>AVERAGE(V44:V54)</f>
+        <v>21.660000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27">
+        <v>20004855</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D27">
+        <v>18242043</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="F27">
+        <v>1414976</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27">
+        <v>410323761</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27">
+        <v>400000000</v>
+      </c>
+      <c r="M27">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28">
+        <v>19171976</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D28">
+        <v>17675400</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F28">
+        <v>1200761</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28">
+        <v>410323761</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28">
+        <v>400000000</v>
+      </c>
+      <c r="M28">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29">
+        <v>18212833</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D29">
+        <v>17282609</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F29">
+        <v>665569</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="H29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29">
+        <v>410323761</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29">
+        <v>400000000</v>
+      </c>
+      <c r="M29">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30">
+        <v>17925306</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D30">
+        <v>17186908</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="F30">
+        <v>516256</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30">
+        <v>410323761</v>
+      </c>
+      <c r="K30" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30">
+        <v>400000000</v>
+      </c>
+      <c r="M30">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31">
+        <v>14152819</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D31">
+        <v>9487587</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="F31">
+        <v>4495409</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31">
+        <v>410323761</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31">
+        <v>400000000</v>
+      </c>
+      <c r="M31">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32">
+        <v>11097326</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D32">
+        <v>8780641</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="F32">
+        <v>2181621</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32">
+        <v>410323761</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32">
+        <v>400000000</v>
+      </c>
+      <c r="M32">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>11082050</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D33">
+        <v>10545531</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F33">
+        <v>431216</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33">
+        <v>410323761</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33">
+        <v>400000000</v>
+      </c>
+      <c r="M33">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>10413886</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D34">
+        <v>9720990</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="F34">
+        <v>519319</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="H34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34">
+        <v>410323761</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34">
+        <v>400000000</v>
+      </c>
+      <c r="M34">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35">
+        <v>9325811</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D35">
+        <v>8815397</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F35">
+        <v>384439</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="H35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35">
+        <v>410323761</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35">
+        <v>400000000</v>
+      </c>
+      <c r="M35">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36">
+        <v>9058408</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D36">
+        <v>7502937</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.83</v>
+      </c>
+      <c r="F36">
+        <v>1431250</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36">
+        <v>410323761</v>
+      </c>
+      <c r="K36" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36">
+        <v>400000000</v>
+      </c>
+      <c r="M36">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37">
+        <v>6597474</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D37">
+        <v>5782722</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="F37">
+        <v>764231</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="H37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37">
+        <v>407509570</v>
+      </c>
+      <c r="K37" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37">
+        <v>400000000</v>
+      </c>
+      <c r="M37">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38">
+        <v>258044026</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="D38">
+        <v>218858977</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="F38">
+        <v>38004318</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>64</v>
+      </c>
+      <c r="J38">
+        <v>407509570</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38">
+        <v>400000000</v>
+      </c>
+      <c r="M38">
+        <v>1.02</v>
+      </c>
+      <c r="U38">
+        <v>424</v>
+      </c>
+      <c r="V38">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <v>94924141</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="D39">
+        <v>87413601</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F39">
+        <v>6436082</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39">
+        <v>407509570</v>
+      </c>
+      <c r="K39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39">
+        <v>400000000</v>
+      </c>
+      <c r="M39">
+        <v>1.02</v>
+      </c>
+      <c r="N39" t="s">
+        <v>197</v>
+      </c>
+      <c r="O39" t="s">
+        <v>253</v>
+      </c>
+      <c r="P39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40">
+        <v>235628368</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="D40">
+        <v>228331424</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F40">
+        <v>5986534</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40">
+        <v>340025766</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40">
+        <v>400000000</v>
+      </c>
+      <c r="M40">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41">
+        <v>87183713</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="D41">
+        <v>83977629</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="F41">
+        <v>2133931</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H41" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" t="s">
+        <v>68</v>
+      </c>
+      <c r="J41">
+        <v>340025766</v>
+      </c>
+      <c r="K41" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41">
+        <v>400000000</v>
+      </c>
+      <c r="M41">
+        <v>0.85</v>
+      </c>
+      <c r="N41" t="s">
+        <v>204</v>
+      </c>
+      <c r="O41" t="s">
+        <v>214</v>
+      </c>
+      <c r="P41" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42">
+        <v>7014408</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D42">
+        <v>6536567</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="F42">
+        <v>411321</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="H42" t="s">
+        <v>45</v>
+      </c>
+      <c r="I42" t="s">
+        <v>68</v>
+      </c>
+      <c r="J42">
+        <v>340025766</v>
+      </c>
+      <c r="K42" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42">
+        <v>400000000</v>
+      </c>
+      <c r="M42">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43">
+        <v>721943446</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.53</v>
+      </c>
+      <c r="D43">
+        <v>707048120</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F43">
+        <v>11240878</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H43" t="s">
+        <v>70</v>
+      </c>
+      <c r="I43" t="s">
+        <v>72</v>
+      </c>
+      <c r="J43">
+        <v>1372260430</v>
+      </c>
+      <c r="K43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L43">
+        <v>1200000000</v>
+      </c>
+      <c r="M43">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N43" t="s">
+        <v>215</v>
+      </c>
+      <c r="O43" t="s">
+        <v>254</v>
+      </c>
+      <c r="P43" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44">
+        <v>590942233</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="D44">
+        <v>575578714</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F44">
+        <v>11891126</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H44" t="s">
+        <v>70</v>
+      </c>
+      <c r="I44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J44">
+        <v>1372260430</v>
+      </c>
+      <c r="K44" t="s">
+        <v>35</v>
+      </c>
+      <c r="L44">
+        <v>1200000000</v>
+      </c>
+      <c r="M44">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N44" t="s">
+        <v>204</v>
+      </c>
+      <c r="O44" t="s">
+        <v>216</v>
+      </c>
+      <c r="P44" t="s">
+        <v>217</v>
+      </c>
+      <c r="U44">
+        <v>442</v>
+      </c>
+      <c r="V44">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>59374751</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D45">
+        <v>57831127</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F45">
+        <v>1221758</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H45" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45">
+        <v>1372260430</v>
+      </c>
+      <c r="K45" t="s">
+        <v>35</v>
+      </c>
+      <c r="L45">
+        <v>1200000000</v>
+      </c>
+      <c r="M45">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46">
+        <v>327514474</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="D46">
+        <v>324239521</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="F46">
+        <v>2800054</v>
+      </c>
+      <c r="G46" s="1">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="H46" t="s">
+        <v>75</v>
+      </c>
+      <c r="I46" t="s">
+        <v>76</v>
+      </c>
+      <c r="J46">
+        <v>515233849</v>
+      </c>
+      <c r="K46" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46">
+        <v>400000000</v>
+      </c>
+      <c r="M46">
+        <v>1.29</v>
+      </c>
+      <c r="N46" t="s">
+        <v>197</v>
+      </c>
+      <c r="O46" t="s">
+        <v>200</v>
+      </c>
+      <c r="P46" t="s">
+        <v>203</v>
+      </c>
+      <c r="U46">
+        <v>400</v>
+      </c>
+      <c r="V46">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47">
+        <v>71466862</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D47">
+        <v>69984629</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F47">
+        <v>1320692</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>76</v>
+      </c>
+      <c r="J47">
+        <v>515233849</v>
+      </c>
+      <c r="K47" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47">
+        <v>400000000</v>
+      </c>
+      <c r="M47">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48">
+        <v>59423002</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="D48">
+        <v>57854568</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F48">
+        <v>1432239</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H48" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" t="s">
+        <v>76</v>
+      </c>
+      <c r="J48">
+        <v>515233849</v>
+      </c>
+      <c r="K48" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48">
+        <v>400000000</v>
+      </c>
+      <c r="M48">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49">
+        <v>52006276</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D49">
+        <v>50849178</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F49">
+        <v>1024171</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" t="s">
+        <v>76</v>
+      </c>
+      <c r="J49">
+        <v>515233849</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49">
+        <v>400000000</v>
+      </c>
+      <c r="M49">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50">
+        <v>4823235</v>
+      </c>
+      <c r="C50" s="1">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="D50">
+        <v>4723283</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F50">
+        <v>91554</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H50" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" t="s">
+        <v>76</v>
+      </c>
+      <c r="J50">
+        <v>515233849</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50">
+        <v>400000000</v>
+      </c>
+      <c r="M50">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51">
+        <v>537333541</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="D51">
+        <v>521991720</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F51">
+        <v>15341821</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s">
+        <v>81</v>
+      </c>
+      <c r="J51">
+        <v>545472174</v>
+      </c>
+      <c r="K51" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51">
+        <v>400000000</v>
+      </c>
+      <c r="M51">
+        <v>1.36</v>
+      </c>
+      <c r="N51" t="s">
+        <v>204</v>
+      </c>
+      <c r="O51" t="s">
+        <v>218</v>
+      </c>
+      <c r="P51" t="s">
+        <v>202</v>
+      </c>
+      <c r="U51">
+        <v>426</v>
+      </c>
+      <c r="V51">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52">
+        <v>8138633</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D52">
+        <v>7773080</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="F52">
+        <v>365553</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="H52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52">
+        <v>545472174</v>
+      </c>
+      <c r="K52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52">
+        <v>400000000</v>
+      </c>
+      <c r="M52">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53">
+        <v>1044135905</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.76419999999999999</v>
+      </c>
+      <c r="D53">
+        <v>1027813078</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.98440000000000005</v>
+      </c>
+      <c r="F53">
+        <v>13189370</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1.26E-2</v>
+      </c>
+      <c r="H53" t="s">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53">
+        <v>1366375755</v>
+      </c>
+      <c r="K53" t="s">
+        <v>35</v>
+      </c>
+      <c r="L53">
+        <v>1200000000</v>
+      </c>
+      <c r="M53">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N53" t="s">
+        <v>197</v>
+      </c>
+      <c r="O53" t="s">
+        <v>219</v>
+      </c>
+      <c r="P53" t="s">
+        <v>219</v>
+      </c>
+      <c r="U53">
+        <v>429</v>
+      </c>
+      <c r="V53">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54">
+        <v>300429527</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.21990000000000001</v>
+      </c>
+      <c r="D54">
+        <v>291057580</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.96879999999999999</v>
+      </c>
+      <c r="F54">
+        <v>3412236</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.14E-2</v>
+      </c>
+      <c r="H54" t="s">
+        <v>75</v>
+      </c>
+      <c r="I54" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54">
+        <v>1366375755</v>
+      </c>
+      <c r="K54" t="s">
+        <v>35</v>
+      </c>
+      <c r="L54">
+        <v>1200000000</v>
+      </c>
+      <c r="M54">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N54" t="s">
+        <v>204</v>
+      </c>
+      <c r="O54" t="s">
+        <v>199</v>
+      </c>
+      <c r="P54" t="s">
+        <v>202</v>
+      </c>
+      <c r="U54">
+        <v>417</v>
+      </c>
+      <c r="V54">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <v>5144843</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3.8E-3</v>
+      </c>
+      <c r="D55">
+        <v>4771263</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.9274</v>
+      </c>
+      <c r="F55">
+        <v>281948</v>
+      </c>
+      <c r="G55" s="1">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="H55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>86</v>
+      </c>
+      <c r="J55">
+        <v>1366375755</v>
+      </c>
+      <c r="K55" t="s">
+        <v>35</v>
+      </c>
+      <c r="L55">
+        <v>1200000000</v>
+      </c>
+      <c r="M55">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56">
+        <v>4258215</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="D56">
+        <v>4053483</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.95189999999999997</v>
+      </c>
+      <c r="F56">
+        <v>140344</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56">
+        <v>1366375755</v>
+      </c>
+      <c r="K56" t="s">
+        <v>35</v>
+      </c>
+      <c r="L56">
+        <v>1200000000</v>
+      </c>
+      <c r="M56">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57">
+        <v>3543390</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="D57">
+        <v>3367652</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.95040000000000002</v>
+      </c>
+      <c r="F57">
+        <v>162485</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="H57" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" t="s">
+        <v>86</v>
+      </c>
+      <c r="J57">
+        <v>1366375755</v>
+      </c>
+      <c r="K57" t="s">
+        <v>35</v>
+      </c>
+      <c r="L57">
+        <v>1200000000</v>
+      </c>
+      <c r="M57">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58">
+        <v>2973052</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="D58">
+        <v>2905871</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.97740000000000005</v>
+      </c>
+      <c r="F58">
+        <v>50375</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="H58" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s">
+        <v>86</v>
+      </c>
+      <c r="J58">
+        <v>1366375755</v>
+      </c>
+      <c r="K58" t="s">
+        <v>35</v>
+      </c>
+      <c r="L58">
+        <v>1200000000</v>
+      </c>
+      <c r="M58">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>105</v>
+      </c>
+      <c r="B59">
+        <v>2530375</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1.9E-3</v>
+      </c>
+      <c r="D59">
+        <v>2464095</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.9738</v>
+      </c>
+      <c r="F59">
+        <v>37318</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1.47E-2</v>
+      </c>
+      <c r="H59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s">
+        <v>86</v>
+      </c>
+      <c r="J59">
+        <v>1366375755</v>
+      </c>
+      <c r="K59" t="s">
+        <v>35</v>
+      </c>
+      <c r="L59">
+        <v>1200000000</v>
+      </c>
+      <c r="M59">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60">
+        <v>2410093</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D60">
+        <v>2328800</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.96630000000000005</v>
+      </c>
+      <c r="F60">
+        <v>55773</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="H60" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" t="s">
+        <v>86</v>
+      </c>
+      <c r="J60">
+        <v>1366375755</v>
+      </c>
+      <c r="K60" t="s">
+        <v>35</v>
+      </c>
+      <c r="L60">
+        <v>1200000000</v>
+      </c>
+      <c r="M60">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61">
+        <v>950355</v>
+      </c>
+      <c r="C61" s="1">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="D61">
+        <v>822024</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="F61">
+        <v>122070</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.12839999999999999</v>
+      </c>
+      <c r="H61" t="s">
+        <v>45</v>
+      </c>
+      <c r="I61" t="s">
+        <v>86</v>
+      </c>
+      <c r="J61">
+        <v>1366375755</v>
+      </c>
+      <c r="K61" t="s">
+        <v>35</v>
+      </c>
+      <c r="L61">
+        <v>1200000000</v>
+      </c>
+      <c r="M61">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62">
+        <v>544596377</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.2772</v>
+      </c>
+      <c r="D62">
+        <v>532853896</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.97840000000000005</v>
+      </c>
+      <c r="F62">
+        <v>6972444</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="H62" t="s">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s">
+        <v>120</v>
+      </c>
+      <c r="J62">
+        <v>1964349544</v>
+      </c>
+      <c r="K62" t="s">
+        <v>121</v>
+      </c>
+      <c r="L62">
+        <v>1800000000</v>
+      </c>
+      <c r="M62">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N62" t="s">
+        <v>204</v>
+      </c>
+      <c r="O62" t="s">
+        <v>199</v>
+      </c>
+      <c r="P62" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63">
+        <v>475432284</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="D63">
+        <v>456058657</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.95930000000000004</v>
+      </c>
+      <c r="F63">
+        <v>16051330</v>
+      </c>
+      <c r="G63" s="1">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="H63" t="s">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s">
+        <v>120</v>
+      </c>
+      <c r="J63">
+        <v>1964349544</v>
+      </c>
+      <c r="K63" t="s">
+        <v>121</v>
+      </c>
+      <c r="L63">
+        <v>1800000000</v>
+      </c>
+      <c r="M63">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N63" t="s">
+        <v>197</v>
+      </c>
+      <c r="O63" t="s">
+        <v>220</v>
+      </c>
+      <c r="P63" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64">
+        <v>408707443</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.20810000000000001</v>
+      </c>
+      <c r="D64">
+        <v>401916727</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="F64">
+        <v>4662402</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1.14E-2</v>
+      </c>
+      <c r="H64" t="s">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s">
+        <v>120</v>
+      </c>
+      <c r="J64">
+        <v>1964349544</v>
+      </c>
+      <c r="K64" t="s">
+        <v>121</v>
+      </c>
+      <c r="L64">
+        <v>1800000000</v>
+      </c>
+      <c r="M64">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N64" t="s">
+        <v>197</v>
+      </c>
+      <c r="O64" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65">
+        <v>333231917</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.1696</v>
+      </c>
+      <c r="D65">
+        <v>274009036</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.82230000000000003</v>
+      </c>
+      <c r="F65">
+        <v>56645110</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="H65" t="s">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s">
+        <v>120</v>
+      </c>
+      <c r="J65">
+        <v>1964349544</v>
+      </c>
+      <c r="K65" t="s">
+        <v>121</v>
+      </c>
+      <c r="L65">
+        <v>1800000000</v>
+      </c>
+      <c r="M65">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N65" t="s">
+        <v>204</v>
+      </c>
+      <c r="O65" t="s">
+        <v>199</v>
+      </c>
+      <c r="P65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66">
+        <v>185308272</v>
+      </c>
+      <c r="C66" s="1">
+        <v>9.4299999999999995E-2</v>
+      </c>
+      <c r="D66">
+        <v>175118959</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="F66">
+        <v>8839473</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H66" t="s">
+        <v>45</v>
+      </c>
+      <c r="I66" t="s">
+        <v>120</v>
+      </c>
+      <c r="J66">
+        <v>1964349544</v>
+      </c>
+      <c r="K66" t="s">
+        <v>121</v>
+      </c>
+      <c r="L66">
+        <v>1800000000</v>
+      </c>
+      <c r="M66">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67">
+        <v>6613976</v>
+      </c>
+      <c r="C67" s="1">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="D67">
+        <v>6297257</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="F67">
+        <v>261844</v>
+      </c>
+      <c r="G67" s="1">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="H67" t="s">
+        <v>49</v>
+      </c>
+      <c r="I67" t="s">
+        <v>120</v>
+      </c>
+      <c r="J67">
+        <v>1964349544</v>
+      </c>
+      <c r="K67" t="s">
+        <v>121</v>
+      </c>
+      <c r="L67">
+        <v>1800000000</v>
+      </c>
+      <c r="M67">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68">
+        <v>5408302</v>
+      </c>
+      <c r="C68" s="1">
+        <v>2.8E-3</v>
+      </c>
+      <c r="D68">
+        <v>5248022</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0.97040000000000004</v>
+      </c>
+      <c r="F68">
+        <v>120414</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2.23E-2</v>
+      </c>
+      <c r="H68" t="s">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s">
+        <v>120</v>
+      </c>
+      <c r="J68">
+        <v>1964349544</v>
+      </c>
+      <c r="K68" t="s">
+        <v>121</v>
+      </c>
+      <c r="L68">
+        <v>1800000000</v>
+      </c>
+      <c r="M68">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69">
+        <v>5050973</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="D69">
+        <v>4828452</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0.95589999999999997</v>
+      </c>
+      <c r="F69">
+        <v>164907</v>
+      </c>
+      <c r="G69" s="1">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="H69" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" t="s">
+        <v>120</v>
+      </c>
+      <c r="J69">
+        <v>1964349544</v>
+      </c>
+      <c r="K69" t="s">
+        <v>121</v>
+      </c>
+      <c r="L69">
+        <v>1800000000</v>
+      </c>
+      <c r="M69">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70">
+        <v>535471455</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.27550000000000002</v>
+      </c>
+      <c r="D70">
+        <v>520544933</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0.97209999999999996</v>
+      </c>
+      <c r="F70">
+        <v>10846509</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="I70" t="s">
+        <v>150</v>
+      </c>
+      <c r="J70">
+        <v>1943641593</v>
+      </c>
+      <c r="K70" t="s">
+        <v>121</v>
+      </c>
+      <c r="L70">
+        <v>1800000000</v>
+      </c>
+      <c r="M70">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71">
+        <v>394719983</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.2031</v>
+      </c>
+      <c r="D71">
+        <v>388047143</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0.98309999999999997</v>
+      </c>
+      <c r="F71">
+        <v>4576757</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="H71" t="s">
+        <v>75</v>
+      </c>
+      <c r="I71" t="s">
+        <v>150</v>
+      </c>
+      <c r="J71">
+        <v>1943641593</v>
+      </c>
+      <c r="K71" t="s">
+        <v>121</v>
+      </c>
+      <c r="L71">
+        <v>1800000000</v>
+      </c>
+      <c r="M71">
+        <v>1.08</v>
+      </c>
+      <c r="N71" t="s">
+        <v>259</v>
+      </c>
+      <c r="O71" t="s">
+        <v>258</v>
+      </c>
+      <c r="P71" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72">
+        <v>304423232</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.15659999999999999</v>
+      </c>
+      <c r="D72">
+        <v>291127436</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0.95630000000000004</v>
+      </c>
+      <c r="F72">
+        <v>10720631</v>
+      </c>
+      <c r="G72" s="1">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="H72" t="s">
+        <v>75</v>
+      </c>
+      <c r="I72" t="s">
+        <v>150</v>
+      </c>
+      <c r="J72">
+        <v>1943641593</v>
+      </c>
+      <c r="K72" t="s">
+        <v>121</v>
+      </c>
+      <c r="L72">
+        <v>1800000000</v>
+      </c>
+      <c r="M72">
+        <v>1.08</v>
+      </c>
+      <c r="N72" t="s">
+        <v>215</v>
+      </c>
+      <c r="O72" t="s">
+        <v>209</v>
+      </c>
+      <c r="P72" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73">
+        <v>278997341</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.14349999999999999</v>
+      </c>
+      <c r="D73">
+        <v>273180736</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0.97919999999999996</v>
+      </c>
+      <c r="F73">
+        <v>3722710</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="H73" t="s">
+        <v>75</v>
+      </c>
+      <c r="I73" t="s">
+        <v>150</v>
+      </c>
+      <c r="J73">
+        <v>1943641593</v>
+      </c>
+      <c r="K73" t="s">
+        <v>121</v>
+      </c>
+      <c r="L73">
+        <v>1800000000</v>
+      </c>
+      <c r="M73">
+        <v>1.08</v>
+      </c>
+      <c r="N73" t="s">
+        <v>197</v>
+      </c>
+      <c r="O73" t="s">
+        <v>224</v>
+      </c>
+      <c r="P73" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74">
+        <v>237905901</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.12239999999999999</v>
+      </c>
+      <c r="D74">
+        <v>229057238</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0.96279999999999999</v>
+      </c>
+      <c r="F74">
+        <v>6560285</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2.76E-2</v>
+      </c>
+      <c r="H74" t="s">
+        <v>75</v>
+      </c>
+      <c r="I74" t="s">
+        <v>150</v>
+      </c>
+      <c r="J74">
+        <v>1943641593</v>
+      </c>
+      <c r="K74" t="s">
+        <v>121</v>
+      </c>
+      <c r="L74">
+        <v>1800000000</v>
+      </c>
+      <c r="M74">
+        <v>1.08</v>
+      </c>
+      <c r="N74" t="s">
+        <v>204</v>
+      </c>
+      <c r="O74" t="s">
+        <v>199</v>
+      </c>
+      <c r="P74" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75">
+        <v>113404883</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="D75">
+        <v>110337736</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="F75">
+        <v>1736954</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="H75" t="s">
+        <v>75</v>
+      </c>
+      <c r="I75" t="s">
+        <v>150</v>
+      </c>
+      <c r="J75">
+        <v>1943641593</v>
+      </c>
+      <c r="K75" t="s">
+        <v>121</v>
+      </c>
+      <c r="L75">
+        <v>1800000000</v>
+      </c>
+      <c r="M75">
+        <v>1.08</v>
+      </c>
+      <c r="N75" t="s">
+        <v>204</v>
+      </c>
+      <c r="O75" t="s">
+        <v>225</v>
+      </c>
+      <c r="P75" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76">
+        <v>63505712</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3.27E-2</v>
+      </c>
+      <c r="D76">
+        <v>62508066</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0.98429999999999995</v>
+      </c>
+      <c r="F76">
+        <v>769410</v>
+      </c>
+      <c r="G76" s="1">
+        <v>1.21E-2</v>
+      </c>
+      <c r="H76" t="s">
+        <v>75</v>
+      </c>
+      <c r="I76" t="s">
+        <v>150</v>
+      </c>
+      <c r="J76">
+        <v>1943641593</v>
+      </c>
+      <c r="K76" t="s">
+        <v>121</v>
+      </c>
+      <c r="L76">
+        <v>1800000000</v>
+      </c>
+      <c r="M76">
+        <v>1.08</v>
+      </c>
+      <c r="N76" t="s">
+        <v>204</v>
+      </c>
+      <c r="O76" t="s">
+        <v>253</v>
+      </c>
+      <c r="P76" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>175</v>
+      </c>
+      <c r="B77">
+        <v>5744443</v>
+      </c>
+      <c r="C77" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D77">
+        <v>5632830</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0.98060000000000003</v>
+      </c>
+      <c r="F77">
+        <v>75371</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="H77" t="s">
+        <v>75</v>
+      </c>
+      <c r="I77" t="s">
+        <v>150</v>
+      </c>
+      <c r="J77">
+        <v>1943641593</v>
+      </c>
+      <c r="K77" t="s">
+        <v>121</v>
+      </c>
+      <c r="L77">
+        <v>1800000000</v>
+      </c>
+      <c r="M77">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>179</v>
+      </c>
+      <c r="B78">
+        <v>5456088</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2.8E-3</v>
+      </c>
+      <c r="D78">
+        <v>5268204</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0.96560000000000001</v>
+      </c>
+      <c r="F78">
+        <v>141514</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="H78" t="s">
+        <v>49</v>
+      </c>
+      <c r="I78" t="s">
+        <v>150</v>
+      </c>
+      <c r="J78">
+        <v>1943641593</v>
+      </c>
+      <c r="K78" t="s">
+        <v>121</v>
+      </c>
+      <c r="L78">
+        <v>1800000000</v>
+      </c>
+      <c r="M78">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>182</v>
+      </c>
+      <c r="B79">
+        <v>4012555</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="D79">
+        <v>3808433</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0.94910000000000005</v>
+      </c>
+      <c r="F79">
+        <v>157189</v>
+      </c>
+      <c r="G79" s="1">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J79">
+        <v>1943641593</v>
+      </c>
+      <c r="K79" t="s">
+        <v>121</v>
+      </c>
+      <c r="L79">
+        <v>1800000000</v>
+      </c>
+      <c r="M79">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>187</v>
+      </c>
+      <c r="B80">
+        <v>910006255</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="D80">
+        <v>886837349</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F80">
+        <v>16637831</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H80" t="s">
+        <v>75</v>
+      </c>
+      <c r="I80" t="s">
+        <v>186</v>
+      </c>
+      <c r="J80">
+        <v>1965498222</v>
+      </c>
+      <c r="K80" t="s">
+        <v>121</v>
+      </c>
+      <c r="L80">
+        <v>1800000000</v>
+      </c>
+      <c r="M80">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N80" t="s">
+        <v>204</v>
+      </c>
+      <c r="O80" t="s">
+        <v>257</v>
+      </c>
+      <c r="P80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>188</v>
+      </c>
+      <c r="B81">
+        <v>555529276</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D81">
+        <v>509954084</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F81">
+        <v>39861581</v>
+      </c>
+      <c r="G81" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H81" t="s">
+        <v>75</v>
+      </c>
+      <c r="I81" t="s">
+        <v>186</v>
+      </c>
+      <c r="J81">
+        <v>1965498222</v>
+      </c>
+      <c r="K81" t="s">
+        <v>121</v>
+      </c>
+      <c r="L81">
+        <v>1800000000</v>
+      </c>
+      <c r="M81">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N81" t="s">
+        <v>204</v>
+      </c>
+      <c r="O81" t="s">
+        <v>227</v>
+      </c>
+      <c r="P81" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>189</v>
+      </c>
+      <c r="B82">
+        <v>335746973</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="D82">
+        <v>309951426</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="F82">
+        <v>22617235</v>
+      </c>
+      <c r="G82" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H82" t="s">
+        <v>75</v>
+      </c>
+      <c r="I82" t="s">
+        <v>186</v>
+      </c>
+      <c r="J82">
+        <v>1965498222</v>
+      </c>
+      <c r="K82" t="s">
+        <v>121</v>
+      </c>
+      <c r="L82">
+        <v>1800000000</v>
+      </c>
+      <c r="M82">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N82" t="s">
+        <v>197</v>
+      </c>
+      <c r="O82" t="s">
+        <v>228</v>
+      </c>
+      <c r="P82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>190</v>
+      </c>
+      <c r="B83">
+        <v>120115260</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="D83">
+        <v>116435613</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="F83">
+        <v>2252448</v>
+      </c>
+      <c r="G83" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I83" t="s">
+        <v>186</v>
+      </c>
+      <c r="J83">
+        <v>1965498222</v>
+      </c>
+      <c r="K83" t="s">
+        <v>121</v>
+      </c>
+      <c r="L83">
+        <v>1800000000</v>
+      </c>
+      <c r="M83">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N83" t="s">
+        <v>215</v>
+      </c>
+      <c r="O83" t="s">
+        <v>214</v>
+      </c>
+      <c r="P83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>191</v>
+      </c>
+      <c r="B84">
+        <v>16366619</v>
+      </c>
+      <c r="C84" s="1">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="D84">
+        <v>10591368</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F84">
+        <v>5468353</v>
+      </c>
+      <c r="G84" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="H84" t="s">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s">
+        <v>186</v>
+      </c>
+      <c r="J84">
+        <v>1965498222</v>
+      </c>
+      <c r="K84" t="s">
+        <v>121</v>
+      </c>
+      <c r="L84">
+        <v>1800000000</v>
+      </c>
+      <c r="M84">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N84" t="s">
+        <v>197</v>
+      </c>
+      <c r="O84" t="s">
+        <v>229</v>
+      </c>
+      <c r="P84" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>192</v>
+      </c>
+      <c r="B85">
+        <v>7169839</v>
+      </c>
+      <c r="C85" s="1">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D85">
+        <v>6842996</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="F85">
+        <v>195008</v>
+      </c>
+      <c r="G85" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="I85" t="s">
+        <v>186</v>
+      </c>
+      <c r="J85">
+        <v>1965498222</v>
+      </c>
+      <c r="K85" t="s">
+        <v>121</v>
+      </c>
+      <c r="L85">
+        <v>1800000000</v>
+      </c>
+      <c r="M85">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>5876187</v>
+      </c>
+      <c r="C86" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D86">
+        <v>5110593</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="F86">
+        <v>715234</v>
+      </c>
+      <c r="G86" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>186</v>
+      </c>
+      <c r="J86">
+        <v>1965498222</v>
+      </c>
+      <c r="K86" t="s">
+        <v>121</v>
+      </c>
+      <c r="L86">
+        <v>1800000000</v>
+      </c>
+      <c r="M86">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87">
+        <v>5838102</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D87">
+        <v>5697176</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="F87">
+        <v>95863</v>
+      </c>
+      <c r="G87" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H87" t="s">
+        <v>75</v>
+      </c>
+      <c r="I87" t="s">
+        <v>186</v>
+      </c>
+      <c r="J87">
+        <v>1965498222</v>
+      </c>
+      <c r="K87" t="s">
+        <v>121</v>
+      </c>
+      <c r="L87">
+        <v>1800000000</v>
+      </c>
+      <c r="M87">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88">
+        <v>4944621</v>
+      </c>
+      <c r="C88" s="1">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="D88">
+        <v>1458755</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F88">
+        <v>3460151</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="H88" t="s">
+        <v>49</v>
+      </c>
+      <c r="I88" t="s">
+        <v>186</v>
+      </c>
+      <c r="J88">
+        <v>1965498222</v>
+      </c>
+      <c r="K88" t="s">
+        <v>121</v>
+      </c>
+      <c r="L88">
+        <v>1800000000</v>
+      </c>
+      <c r="M88">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89">
+        <v>3905090</v>
+      </c>
+      <c r="C89" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="D89">
+        <v>3673828</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="F89">
+        <v>179654</v>
+      </c>
+      <c r="G89" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>186</v>
+      </c>
+      <c r="J89">
+        <v>1965498222</v>
+      </c>
+      <c r="K89" t="s">
+        <v>121</v>
+      </c>
+      <c r="L89">
+        <v>1800000000</v>
+      </c>
+      <c r="M89">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90">
+        <v>1126600791</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.79810000000000003</v>
+      </c>
+      <c r="D90">
+        <v>1108945422</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0.98429999999999995</v>
+      </c>
+      <c r="F90">
+        <v>12920710</v>
+      </c>
+      <c r="G90" s="1">
+        <v>1.15E-2</v>
+      </c>
+      <c r="H90" t="s">
+        <v>75</v>
+      </c>
+      <c r="I90" t="s">
+        <v>245</v>
+      </c>
+      <c r="J90">
+        <v>1411581699</v>
+      </c>
+      <c r="K90" t="s">
+        <v>35</v>
+      </c>
+      <c r="L90">
+        <v>1200000000</v>
+      </c>
+      <c r="M90">
+        <v>1.18</v>
+      </c>
+      <c r="N90" t="s">
+        <v>247</v>
+      </c>
+      <c r="O90" t="s">
+        <v>246</v>
+      </c>
+      <c r="P90" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91">
+        <v>249005691</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.1764</v>
+      </c>
+      <c r="D91">
+        <v>242619689</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0.97440000000000004</v>
+      </c>
+      <c r="F91">
+        <v>4898776</v>
+      </c>
+      <c r="G91" s="1">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="H91" t="s">
+        <v>75</v>
+      </c>
+      <c r="I91" t="s">
+        <v>245</v>
+      </c>
+      <c r="J91">
+        <v>1411581699</v>
+      </c>
+      <c r="K91" t="s">
+        <v>35</v>
+      </c>
+      <c r="L91">
+        <v>1200000000</v>
+      </c>
+      <c r="M91">
+        <v>1.18</v>
+      </c>
+      <c r="N91" t="s">
+        <v>197</v>
+      </c>
+      <c r="O91" t="s">
+        <v>252</v>
+      </c>
+      <c r="P91" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92">
+        <v>8797450</v>
+      </c>
+      <c r="C92" s="1">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="D92">
+        <v>8322860</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0.94610000000000005</v>
+      </c>
+      <c r="F92">
+        <v>435219</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="H92" t="s">
+        <v>75</v>
+      </c>
+      <c r="I92" t="s">
+        <v>245</v>
+      </c>
+      <c r="J92">
+        <v>1411581699</v>
+      </c>
+      <c r="K92" t="s">
+        <v>35</v>
+      </c>
+      <c r="L92">
+        <v>1200000000</v>
+      </c>
+      <c r="M92">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93">
+        <v>5622155</v>
+      </c>
+      <c r="C93" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D93">
+        <v>4734151</v>
+      </c>
+      <c r="E93" s="1">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="F93">
+        <v>869099</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="H93" t="s">
+        <v>49</v>
+      </c>
+      <c r="I93" t="s">
+        <v>245</v>
+      </c>
+      <c r="J93">
+        <v>1411581699</v>
+      </c>
+      <c r="K93" t="s">
+        <v>35</v>
+      </c>
+      <c r="L93">
+        <v>1200000000</v>
+      </c>
+      <c r="M93">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>240</v>
+      </c>
+      <c r="B94">
+        <v>5125817</v>
+      </c>
+      <c r="C94" s="1">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D94">
+        <v>2227969</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0.43469999999999998</v>
+      </c>
+      <c r="F94">
+        <v>2890376</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.56389999999999996</v>
+      </c>
+      <c r="H94" t="s">
+        <v>75</v>
+      </c>
+      <c r="I94" t="s">
+        <v>245</v>
+      </c>
+      <c r="J94">
+        <v>1411581699</v>
+      </c>
+      <c r="K94" t="s">
+        <v>35</v>
+      </c>
+      <c r="L94">
+        <v>1200000000</v>
+      </c>
+      <c r="M94">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>241</v>
+      </c>
+      <c r="B95">
+        <v>5119461</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="D95">
+        <v>4853312</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="F95">
+        <v>256674</v>
+      </c>
+      <c r="G95" s="1">
+        <v>5.0099999999999999E-2</v>
+      </c>
+      <c r="H95" t="s">
+        <v>75</v>
+      </c>
+      <c r="I95" t="s">
+        <v>245</v>
+      </c>
+      <c r="J95">
+        <v>1411581699</v>
+      </c>
+      <c r="K95" t="s">
+        <v>35</v>
+      </c>
+      <c r="L95">
+        <v>1200000000</v>
+      </c>
+      <c r="M95">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>242</v>
+      </c>
+      <c r="B96">
+        <v>4064941</v>
+      </c>
+      <c r="C96" s="1">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="D96">
+        <v>1579567</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0.3886</v>
+      </c>
+      <c r="F96">
+        <v>2478956</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.60980000000000001</v>
+      </c>
+      <c r="H96" t="s">
+        <v>75</v>
+      </c>
+      <c r="I96" t="s">
+        <v>245</v>
+      </c>
+      <c r="J96">
+        <v>1411581699</v>
+      </c>
+      <c r="K96" t="s">
+        <v>35</v>
+      </c>
+      <c r="L96">
+        <v>1200000000</v>
+      </c>
+      <c r="M96">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>243</v>
+      </c>
+      <c r="B97">
+        <v>3823562</v>
+      </c>
+      <c r="C97" s="1">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="D97">
+        <v>3693485</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="F97">
+        <v>110915</v>
+      </c>
+      <c r="G97" s="1">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H97" t="s">
+        <v>75</v>
+      </c>
+      <c r="I97" t="s">
+        <v>245</v>
+      </c>
+      <c r="J97">
+        <v>1411581699</v>
+      </c>
+      <c r="K97" t="s">
+        <v>35</v>
+      </c>
+      <c r="L97">
+        <v>1200000000</v>
+      </c>
+      <c r="M97">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>244</v>
+      </c>
+      <c r="B98">
+        <v>3421831</v>
+      </c>
+      <c r="C98" s="1">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D98">
+        <v>1322892</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0.3866</v>
+      </c>
+      <c r="F98">
+        <v>1934994</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.5655</v>
+      </c>
+      <c r="H98" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" t="s">
+        <v>245</v>
+      </c>
+      <c r="J98">
+        <v>1411581699</v>
+      </c>
+      <c r="K98" t="s">
+        <v>35</v>
+      </c>
+      <c r="L98">
+        <v>1200000000</v>
+      </c>
+      <c r="M98">
+        <v>1.18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>